--- a/data/random_collections/TabS2_primeseq_prices.xlsx
+++ b/data/random_collections/TabS2_primeseq_prices.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\briem\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\prime-seq_NextGen\data\random_collections\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="142">
   <si>
     <t>Reagents:</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>total cost [€]</t>
+  </si>
+  <si>
+    <t>in USD</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -910,6 +913,7 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,7 +1129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="70.5703125" bestFit="1" customWidth="1"/>
@@ -1140,13 +1144,13 @@
     <col min="15" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1">
+    <row r="1" spans="1:14" ht="15.75" thickBot="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
@@ -1185,7 +1189,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="31" t="s">
         <v>11</v>
       </c>
@@ -1228,7 +1232,7 @@
         <v>1.0641114200000001</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" s="31" t="s">
         <v>11</v>
       </c>
@@ -1271,7 +1275,7 @@
         <v>0.62144820766666653</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" thickBot="1">
+    <row r="5" spans="1:14" ht="15.75" thickBot="1">
       <c r="A5" s="31" t="s">
         <v>11</v>
       </c>
@@ -1314,7 +1318,7 @@
         <v>78.824136907199517</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" thickBot="1">
+    <row r="6" spans="1:14" ht="15.75" thickBot="1">
       <c r="A6" s="31" t="s">
         <v>19</v>
       </c>
@@ -1347,7 +1351,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="31" t="s">
         <v>23</v>
       </c>
@@ -1383,8 +1387,11 @@
         <v>136</v>
       </c>
       <c r="M7" s="49"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="31" t="s">
         <v>25</v>
       </c>
@@ -1422,8 +1429,11 @@
       <c r="M8" s="36">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="31" t="s">
         <v>27</v>
       </c>
@@ -1462,7 +1472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" s="31" t="s">
         <v>29</v>
       </c>
@@ -1498,8 +1508,12 @@
         <f>($M$8*($M$3+$M$4))+($M$9*$M$5)</f>
         <v>240.63786116319952</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="50">
+        <f>M10*$N$8</f>
+        <v>279.13991894931144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="31" t="s">
         <v>32</v>
       </c>
@@ -1538,8 +1552,12 @@
         <f>M10/$M$8</f>
         <v>2.5066443871166615</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="50">
+        <f t="shared" ref="N11:N13" si="1">M11*$N$8</f>
+        <v>2.9077074890553272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="31" t="s">
         <v>35</v>
       </c>
@@ -1565,7 +1583,7 @@
         <v>59</v>
       </c>
       <c r="I12" s="41">
-        <f t="shared" ref="I12:I15" si="1">F12/D12*G12</f>
+        <f t="shared" ref="I12:I15" si="2">F12/D12*G12</f>
         <v>5.3215999999999999E-2</v>
       </c>
       <c r="J12" s="31" t="s">
@@ -1578,8 +1596,12 @@
         <f>($M$8*$M$4)+($M$9*$M$5)</f>
         <v>138.48316484319952</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1">
+      <c r="N12" s="50">
+        <f t="shared" si="1"/>
+        <v>160.64047121811143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickBot="1">
       <c r="A13" s="31" t="s">
         <v>38</v>
       </c>
@@ -1605,7 +1627,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.4500000000000005E-2</v>
       </c>
       <c r="J13" s="31" t="s">
@@ -1618,8 +1640,12 @@
         <f>M12/$M$8</f>
         <v>1.4425329671166616</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="50">
+        <f t="shared" si="1"/>
+        <v>1.6733382418553273</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="31" t="s">
         <v>40</v>
       </c>
@@ -1646,14 +1672,14 @@
         <v>34</v>
       </c>
       <c r="I14" s="41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.2526041666666665E-2</v>
       </c>
       <c r="J14" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" s="31" t="s">
         <v>42</v>
       </c>
@@ -1680,7 +1706,7 @@
         <v>34</v>
       </c>
       <c r="I15" s="41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.53</v>
       </c>
       <c r="J15" s="31" t="s">
@@ -1688,7 +1714,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" s="31" t="s">
         <v>44</v>
       </c>
@@ -1744,7 +1770,7 @@
         <v>34</v>
       </c>
       <c r="I17" s="41">
-        <f t="shared" ref="I17:I27" si="2">F17/D17*G17</f>
+        <f t="shared" ref="I17:I27" si="3">F17/D17*G17</f>
         <v>1.2669587628865981</v>
       </c>
       <c r="J17" s="31" t="s">
@@ -1779,7 +1805,7 @@
         <v>13</v>
       </c>
       <c r="I18" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.3088</v>
       </c>
       <c r="J18" s="31" t="s">
@@ -1814,7 +1840,7 @@
         <v>13</v>
       </c>
       <c r="I19" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.8204800000000001</v>
       </c>
       <c r="J19" s="31" t="s">
@@ -1848,7 +1874,7 @@
         <v>56</v>
       </c>
       <c r="I20" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>29.5</v>
       </c>
       <c r="J20" s="31" t="s">
@@ -1881,7 +1907,7 @@
         <v>59</v>
       </c>
       <c r="I21" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.6336998131121494E-2</v>
       </c>
       <c r="J21" s="29" t="s">
@@ -1917,7 +1943,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2969288000000001E-2</v>
       </c>
       <c r="J22" s="29" t="s">
@@ -1950,7 +1976,7 @@
         <v>63</v>
       </c>
       <c r="I23" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.4250000000000011E-3</v>
       </c>
       <c r="J23" s="31" t="s">
@@ -1984,7 +2010,7 @@
         <v>63</v>
       </c>
       <c r="I24" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.1900000000000003E-3</v>
       </c>
       <c r="J24" s="31" t="s">
@@ -2018,7 +2044,7 @@
         <v>13</v>
       </c>
       <c r="I25" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.0608000000000002E-3</v>
       </c>
       <c r="J25" s="29" t="s">
@@ -2052,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="I26" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.195264E-2</v>
       </c>
       <c r="J26" s="29" t="s">
@@ -2086,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="I27" s="41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.7303999999999995</v>
       </c>
       <c r="J27" s="29" t="s">
@@ -2116,7 +2142,7 @@
         <v>13</v>
       </c>
       <c r="I28" s="41">
-        <f t="shared" ref="I28:I31" si="3">F28/D28*G28</f>
+        <f t="shared" ref="I28:I31" si="4">F28/D28*G28</f>
         <v>9.6941880000000008E-2</v>
       </c>
       <c r="J28" s="29" t="s">
@@ -2145,7 +2171,7 @@
         <v>13</v>
       </c>
       <c r="I29" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.0775200000000003E-2</v>
       </c>
       <c r="J29" s="29" t="s">
@@ -2174,7 +2200,7 @@
         <v>13</v>
       </c>
       <c r="I30" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.9920000000000017E-4</v>
       </c>
       <c r="J30" s="29" t="s">
@@ -2207,7 +2233,7 @@
         <v>129</v>
       </c>
       <c r="I31" s="41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.9</v>
       </c>
       <c r="J31" s="29" t="s">
@@ -2351,7 +2377,7 @@
         <v>3</v>
       </c>
       <c r="I37" s="43">
-        <f t="shared" ref="I37:I42" si="4">H37*G37</f>
+        <f t="shared" ref="I37:I42" si="5">H37*G37</f>
         <v>7.4195999999999991</v>
       </c>
       <c r="J37" s="29" t="s">
@@ -2385,7 +2411,7 @@
         <v>16</v>
       </c>
       <c r="I38" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.4480000000000004</v>
       </c>
       <c r="J38" s="29" t="s">
@@ -2419,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="I39" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.4598</v>
       </c>
       <c r="J39" s="29" t="s">
@@ -2451,7 +2477,7 @@
         <v>20</v>
       </c>
       <c r="I40" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.77</v>
       </c>
       <c r="J40" s="29" t="s">
@@ -2483,7 +2509,7 @@
         <v>2</v>
       </c>
       <c r="I41" s="43">
-        <f t="shared" ref="I41" si="5">H41*G41</f>
+        <f t="shared" ref="I41" si="6">H41*G41</f>
         <v>7.6999999999999999E-2</v>
       </c>
       <c r="J41" s="29" t="s">
@@ -2515,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="I42" s="43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.77</v>
       </c>
       <c r="J42" s="29" t="s">
@@ -2582,7 +2608,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="43">
-        <f t="shared" ref="I44:I46" si="6">H44*G44</f>
+        <f t="shared" ref="I44:I46" si="7">H44*G44</f>
         <v>0.503</v>
       </c>
       <c r="J44" s="29" t="s">
@@ -2616,7 +2642,7 @@
         <v>10</v>
       </c>
       <c r="I45" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.50800000000000001</v>
       </c>
       <c r="J45" s="29" t="s">
@@ -2648,7 +2674,7 @@
         <v>5</v>
       </c>
       <c r="I46" s="43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.1624999999999996</v>
       </c>
       <c r="J46" s="29" t="s">
